--- a/artfynd/A 14466-2026 artfynd.xlsx
+++ b/artfynd/A 14466-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102977693</v>
+        <v>96355272</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+          <t>Lejdet, 3 km VNV om Stavby kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662395.0530995501</v>
+        <v>662419</v>
       </c>
       <c r="R2" t="n">
-        <v>6657620.532294132</v>
+        <v>6657637</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +755,9 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,15 +770,45 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Granskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies subsp. abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
+          <t>Thorleif Joelson, Henry Åkerström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,15 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102977694</v>
+        <v>102977510</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,37 +830,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+          <t>Stavby kyrka, 3,2 km NV-ut, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662393.2908850419</v>
+        <v>662424</v>
       </c>
       <c r="R3" t="n">
-        <v>6657660.49506754</v>
+        <v>6657642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +901,14 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Unga sporkapslar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,9 +917,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -915,56 +949,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102977465</v>
+        <v>102977511</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+          <t>Stavby kyrka, 3,2 km NV-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662395.0530995501</v>
+        <v>662424</v>
       </c>
       <c r="R4" t="n">
-        <v>6657620.532294132</v>
+        <v>6657642</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,19 +1022,9 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,6 +1036,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1038,12 +1069,7 @@
         <v>102977506</v>
       </c>
       <c r="B5" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,7 +1091,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1105,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662394.5684892939</v>
+        <v>662395</v>
       </c>
       <c r="R5" t="n">
-        <v>6657631.522099941</v>
+        <v>6657631</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,19 +1138,9 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,15 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102977463</v>
+        <v>102977507</v>
       </c>
       <c r="B6" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,24 +1193,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222002</v>
+        <v>2668</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1209,13 +1221,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662395.0530995501</v>
+        <v>662387</v>
       </c>
       <c r="R6" t="n">
-        <v>6657620.532294132</v>
+        <v>6657648</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,30 +1254,29 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1286,15 +1297,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102977507</v>
+        <v>102977508</v>
       </c>
       <c r="B7" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,38 +1308,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2668</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662386.3139374861</v>
+        <v>662424</v>
       </c>
       <c r="R7" t="n">
-        <v>6657648.175317946</v>
+        <v>6657654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,21 +1370,11 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1389,12 +1386,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Block (&gt; 200 mm)</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>Wood surface of dead wood</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1416,15 +1413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102977464</v>
+        <v>102977694</v>
       </c>
       <c r="B8" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,26 +1424,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1459,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662395.0530995501</v>
+        <v>662394</v>
       </c>
       <c r="R8" t="n">
-        <v>6657620.532294132</v>
+        <v>6657660</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1492,19 +1484,9 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,6 +1511,650 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96355169</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lejdet, 3 km VNV om Stavby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>662413</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6657597</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102977693</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>662395</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6657620</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102977464</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>662395</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6657620</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>102977463</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>662395</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6657620</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>102977465</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>662395</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6657620</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>102977466</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stavby kyrka, 3,3 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>662424</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6657642</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
